--- a/cet4/result/34_校园音乐_钢琴少女的逆袭之路/34_校园音乐_钢琴少女的逆袭之路_学习版.xlsx
+++ b/cet4/result/34_校园音乐_钢琴少女的逆袭之路/34_校园音乐_钢琴少女的逆袭之路_学习版.xlsx
@@ -397,843 +397,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D41"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>leaf</v>
       </c>
       <c r="B2" t="str">
-        <v>leaf</v>
+        <v>/liːf/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>叶子</v>
       </c>
-      <c r="D2" t="str">
-        <v>leaf(叶子)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>library</v>
       </c>
       <c r="B3" t="str">
-        <v>library</v>
+        <v>/ˈlaɪbreri/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>图书馆</v>
       </c>
-      <c r="D3" t="str">
-        <v>library(图书馆)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>brilliant</v>
       </c>
       <c r="B4" t="str">
-        <v>brilliant</v>
+        <v>/ˈbrɪliənt/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>杰出的</v>
       </c>
-      <c r="D4" t="str">
-        <v>brilliant(杰出的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>recite</v>
       </c>
       <c r="B5" t="str">
-        <v>recite</v>
+        <v>/rɪˈsaɪt/</v>
       </c>
       <c r="C5" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>背诵</v>
       </c>
-      <c r="D5" t="str">
-        <v>recite(背诵)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>concentration</v>
       </c>
       <c r="B6" t="str">
-        <v>concentration</v>
+        <v>/ˌkɑːnsnˈtreɪʃn/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>专心</v>
       </c>
-      <c r="D6" t="str">
-        <v>concentration(专心)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>sportsman</v>
       </c>
       <c r="B7" t="str">
-        <v>sportsman</v>
+        <v>/ˈspɔːrtsmən/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>运动员</v>
       </c>
-      <c r="D7" t="str">
-        <v>sportsman(运动员)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>appointment</v>
       </c>
       <c r="B8" t="str">
-        <v>appointment</v>
+        <v>/əˈpɔɪntmənt/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>约定</v>
       </c>
-      <c r="D8" t="str">
-        <v>appointment(约定)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>station</v>
       </c>
       <c r="B9" t="str">
-        <v>station</v>
+        <v>/ˈsteɪʃn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D9" t="str">
         <v>车站</v>
       </c>
-      <c r="D9" t="str">
-        <v>station(车站)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>jewish</v>
       </c>
       <c r="B10" t="str">
-        <v>jewish</v>
+        <v>/ˈdʒuːɪʃ/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>犹太</v>
       </c>
-      <c r="D10" t="str">
-        <v>jewish(犹太)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>via</v>
       </c>
       <c r="B11" t="str">
-        <v>via</v>
+        <v>/ˈvaɪə,ˈviːə/</v>
       </c>
       <c r="C11" t="str">
+        <v>prep.</v>
+      </c>
+      <c r="D11" t="str">
         <v>经由</v>
       </c>
-      <c r="D11" t="str">
-        <v>via(经由)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>upright</v>
       </c>
       <c r="B12" t="str">
-        <v>upright</v>
+        <v>/ˈʌpraɪt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>正直的</v>
       </c>
-      <c r="D12" t="str">
-        <v>upright(正直的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>the</v>
       </c>
       <c r="B13" t="str">
-        <v>the</v>
+        <v>/ðə; ði; ðiː/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./adv./art.</v>
+      </c>
+      <c r="D13" t="str">
         <v>那位</v>
       </c>
-      <c r="D13" t="str">
-        <v>the(那位)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>lorry</v>
       </c>
       <c r="B14" t="str">
-        <v>lorry</v>
+        <v>/ˈlɔːri/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>卡车</v>
       </c>
-      <c r="D14" t="str">
-        <v>lorry(卡车)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>dorm</v>
       </c>
       <c r="B15" t="str">
-        <v>dorm</v>
+        <v>/dɔːrm/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>宿舍</v>
       </c>
-      <c r="D15" t="str">
-        <v>dorm(宿舍)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>knee</v>
       </c>
       <c r="B16" t="str">
-        <v>knee</v>
+        <v>/niː/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D16" t="str">
         <v>膝盖</v>
       </c>
-      <c r="D16" t="str">
-        <v>knee(膝盖)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>rock</v>
       </c>
       <c r="B17" t="str">
-        <v>rock</v>
+        <v>/rɑːk/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>摇滚</v>
       </c>
-      <c r="D17" t="str">
-        <v>rock(摇滚)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>fair</v>
       </c>
       <c r="B18" t="str">
-        <v>fair</v>
+        <v>/fer/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vi./v./adj./adv.</v>
+      </c>
+      <c r="D18" t="str">
         <v>展览会</v>
       </c>
-      <c r="D18" t="str">
-        <v>fair(展览会)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>internal</v>
       </c>
       <c r="B19" t="str">
-        <v>internal</v>
+        <v>/ɪnˈtɜːrnl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>内部</v>
       </c>
-      <c r="D19" t="str">
-        <v>internal(内部)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>erect</v>
       </c>
       <c r="B20" t="str">
-        <v>erect</v>
+        <v>/ɪˈrekt/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>竖立</v>
       </c>
-      <c r="D20" t="str">
-        <v>erect(竖立)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>label</v>
       </c>
       <c r="B21" t="str">
-        <v>rock</v>
+        <v>/ˈleɪbl/</v>
       </c>
       <c r="C21" t="str">
-        <v>岩石</v>
+        <v>n./vt.</v>
       </c>
       <c r="D21" t="str">
-        <v>rock(岩石)📢</v>
+        <v>标签</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>bay</v>
       </c>
       <c r="B22" t="str">
-        <v>label</v>
+        <v>/beɪ/</v>
       </c>
       <c r="C22" t="str">
-        <v>标签</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>label(标签)📢</v>
+        <v>海湾</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>actual</v>
       </c>
       <c r="B23" t="str">
-        <v>label</v>
+        <v>/ˈæktʃuəl/</v>
       </c>
       <c r="C23" t="str">
-        <v>标签</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>label(标签)📢</v>
+        <v>实际的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>comprehension</v>
       </c>
       <c r="B24" t="str">
-        <v>bay</v>
+        <v>/ˌkɑːmprɪˈhenʃn/</v>
       </c>
       <c r="C24" t="str">
-        <v>海湾</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>bay(海湾)📢</v>
+        <v>理解</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>amuse</v>
       </c>
       <c r="B25" t="str">
-        <v>library</v>
+        <v>/əˈmjuːz/</v>
       </c>
       <c r="C25" t="str">
-        <v>图书馆</v>
+        <v>vt.</v>
       </c>
       <c r="D25" t="str">
-        <v>library(图书馆)📢</v>
+        <v>逗乐</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>process</v>
       </c>
       <c r="B26" t="str">
-        <v>actual</v>
+        <v>/'prɑses/</v>
       </c>
       <c r="C26" t="str">
-        <v>实际的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>actual(实际的)📢</v>
+        <v>过程</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>temperature</v>
       </c>
       <c r="B27" t="str">
-        <v>comprehension</v>
+        <v>/ˈtemprətʃər,ˈtemprətʃʊr/</v>
       </c>
       <c r="C27" t="str">
-        <v>理解</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>comprehension(理解)📢</v>
+        <v>体温</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>potential</v>
       </c>
       <c r="B28" t="str">
-        <v>amuse</v>
+        <v>/pəˈtenʃl/</v>
       </c>
       <c r="C28" t="str">
-        <v>逗乐</v>
+        <v>n./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>amuse(逗乐)📢</v>
+        <v>潜力</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>rhythm</v>
       </c>
       <c r="B29" t="str">
-        <v>process</v>
+        <v>/ˈrɪðəm/</v>
       </c>
       <c r="C29" t="str">
-        <v>过程</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>process(过程)📢</v>
+        <v>节奏</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>similar</v>
       </c>
       <c r="B30" t="str">
-        <v>temperature</v>
+        <v>/ˈsɪmələr/</v>
       </c>
       <c r="C30" t="str">
-        <v>体温</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>temperature(体温)📢</v>
+        <v>相似的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>island</v>
       </c>
       <c r="B31" t="str">
-        <v>internal</v>
+        <v>/ˈaɪlənd/</v>
       </c>
       <c r="C31" t="str">
-        <v>内心</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>internal(内心)📢</v>
+        <v>岛</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>connection</v>
       </c>
       <c r="B32" t="str">
-        <v>potential</v>
+        <v>/kəˈnekʃn/</v>
       </c>
       <c r="C32" t="str">
-        <v>潜力</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>potential(潜力)📢</v>
+        <v>连接</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>sticky</v>
       </c>
       <c r="B33" t="str">
-        <v>rhythm</v>
+        <v>/ˈstɪki/</v>
       </c>
       <c r="C33" t="str">
-        <v>节奏</v>
+        <v>adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>rhythm(节奏)📢</v>
+        <v>棘手的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>domestic</v>
       </c>
       <c r="B34" t="str">
-        <v>process</v>
+        <v>/dəˈmestɪk/</v>
       </c>
       <c r="C34" t="str">
-        <v>过程</v>
+        <v>n./adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>process(过程)📢</v>
+        <v>国内的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>drag</v>
       </c>
       <c r="B35" t="str">
-        <v>similar</v>
+        <v>/dræɡ/</v>
       </c>
       <c r="C35" t="str">
-        <v>相似的</v>
+        <v>n./v.</v>
       </c>
       <c r="D35" t="str">
-        <v>similar(相似的)📢</v>
+        <v>拖延</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>fountain</v>
       </c>
       <c r="B36" t="str">
-        <v>island</v>
+        <v>/ˈfaʊntn/</v>
       </c>
       <c r="C36" t="str">
-        <v>岛</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>island(岛)📢</v>
+        <v>喷泉</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>signature</v>
       </c>
       <c r="B37" t="str">
-        <v>bay</v>
+        <v>/ˈsɪɡnətʃər/</v>
       </c>
       <c r="C37" t="str">
-        <v>海湾</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>bay(海湾)📢</v>
+        <v>签名</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>choose</v>
       </c>
       <c r="B38" t="str">
-        <v>internal</v>
+        <v>/tʃuːz/</v>
       </c>
       <c r="C38" t="str">
-        <v>内心</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>internal(内心)📢</v>
+        <v>选择</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>stain</v>
       </c>
       <c r="B39" t="str">
-        <v>connection</v>
+        <v>/steɪn/</v>
       </c>
       <c r="C39" t="str">
-        <v>连接</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>connection(连接)📢</v>
+        <v>玷污</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>acceptable</v>
       </c>
       <c r="B40" t="str">
-        <v>sticky</v>
+        <v>/əkˈseptəbl/</v>
       </c>
       <c r="C40" t="str">
-        <v>棘手的</v>
+        <v>adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>sticky(棘手的)📢</v>
+        <v>可接受的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>liquor</v>
       </c>
       <c r="B41" t="str">
-        <v>domestic</v>
+        <v>/ˈlɪkər/</v>
       </c>
       <c r="C41" t="str">
-        <v>国内的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>domestic(国内的)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>drag</v>
-      </c>
-      <c r="C42" t="str">
-        <v>拖延</v>
-      </c>
-      <c r="D42" t="str">
-        <v>drag(拖延)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>via</v>
-      </c>
-      <c r="C43" t="str">
-        <v>经由</v>
-      </c>
-      <c r="D43" t="str">
-        <v>via(经由)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>fountain</v>
-      </c>
-      <c r="C44" t="str">
-        <v>喷泉</v>
-      </c>
-      <c r="D44" t="str">
-        <v>fountain(喷泉)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>signature</v>
-      </c>
-      <c r="C45" t="str">
-        <v>签名</v>
-      </c>
-      <c r="D45" t="str">
-        <v>signature(签名)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>brilliant</v>
-      </c>
-      <c r="C46" t="str">
-        <v>杰出的</v>
-      </c>
-      <c r="D46" t="str">
-        <v>brilliant(杰出的)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>bay</v>
-      </c>
-      <c r="C47" t="str">
-        <v>海湾</v>
-      </c>
-      <c r="D47" t="str">
-        <v>bay(海湾)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>rock</v>
-      </c>
-      <c r="C48" t="str">
-        <v>岩石</v>
-      </c>
-      <c r="D48" t="str">
-        <v>rock(岩石)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>choose</v>
-      </c>
-      <c r="C49" t="str">
-        <v>选择</v>
-      </c>
-      <c r="D49" t="str">
-        <v>choose(选择)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>stain</v>
-      </c>
-      <c r="C50" t="str">
-        <v>玷污</v>
-      </c>
-      <c r="D50" t="str">
-        <v>stain(玷污)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>acceptable</v>
-      </c>
-      <c r="C51" t="str">
-        <v>可接受的</v>
-      </c>
-      <c r="D51" t="str">
-        <v>acceptable(可接受的)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>liquor</v>
-      </c>
-      <c r="C52" t="str">
         <v>酒</v>
-      </c>
-      <c r="D52" t="str">
-        <v>liquor(酒)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>library</v>
-      </c>
-      <c r="C53" t="str">
-        <v>图书馆</v>
-      </c>
-      <c r="D53" t="str">
-        <v>library(图书馆)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>process</v>
-      </c>
-      <c r="C54" t="str">
-        <v>过程</v>
-      </c>
-      <c r="D54" t="str">
-        <v>process(过程)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>leaf</v>
-      </c>
-      <c r="C55" t="str">
-        <v>叶子</v>
-      </c>
-      <c r="D55" t="str">
-        <v>leaf(叶子)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>choose</v>
-      </c>
-      <c r="C56" t="str">
-        <v>选择</v>
-      </c>
-      <c r="D56" t="str">
-        <v>choose(选择)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>fountain</v>
-      </c>
-      <c r="C57" t="str">
-        <v>喷泉</v>
-      </c>
-      <c r="D57" t="str">
-        <v>fountain(喷泉)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>rock</v>
-      </c>
-      <c r="C58" t="str">
-        <v>岩石</v>
-      </c>
-      <c r="D58" t="str">
-        <v>rock(岩石)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>bay</v>
-      </c>
-      <c r="C59" t="str">
-        <v>海湾</v>
-      </c>
-      <c r="D59" t="str">
-        <v>bay(海湾)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
   </ignoredErrors>
 </worksheet>
 </file>